--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,147 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120089618</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bockmossen, Virsbo, , Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557879</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6632746</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skrämde tjädern, den flög upp från marken bland blåbärsrisen och flög i riktning NÖ mot Bockmossen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,6 +1203,131 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120143957</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bockmossen, Virsbo, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6632899</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120089618</v>
+        <v>120143957</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,57 +1080,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bockmossen, Virsbo, , Vstm</t>
+          <t>Bockmossen, Virsbo, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557879</v>
+        <v>558021</v>
       </c>
       <c r="R5" t="n">
-        <v>6632746</v>
+        <v>6632899</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1172,19 +1159,20 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Skrämde tjädern, den flög upp från marken bland blåbärsrisen och flög i riktning NÖ mot Bockmossen.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1197,22 +1185,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120143957</v>
+        <v>120089618</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1221,44 +1205,57 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bockmossen, Virsbo, Vstm, Vstm</t>
+          <t>Bockmossen, Virsbo, , Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558021</v>
+        <v>557879</v>
       </c>
       <c r="R6" t="n">
-        <v>6632899</v>
+        <v>6632746</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1300,20 +1297,19 @@
           <t>13:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skrämde tjädern, den flög upp från marken bland blåbärsrisen och flög i riktning NÖ mot Bockmossen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1326,7 +1322,11 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>120143957</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>120089618</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,1151 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122485461</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90851</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557922</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6632643</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122485467</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91413</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>557835</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6633054</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122485471</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92114</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558027</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6632721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122485472</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80613</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6633116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122485460</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91453</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557653</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6632924</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Granskog, sumpskogsstråk</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122485476</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6632935</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122485481</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98240</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557818</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122485470</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92126</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558025</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6632894</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122485466</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557665</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6633121</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122485475</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>557534</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6632977</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Kvist av gammal gran</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485461</v>
+        <v>122485466</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557922</v>
+        <v>557665</v>
       </c>
       <c r="R7" t="n">
-        <v>6632643</v>
+        <v>6633121</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485467</v>
+        <v>122485481</v>
       </c>
       <c r="B8" t="n">
-        <v>91413</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557835</v>
+        <v>557818</v>
       </c>
       <c r="R8" t="n">
-        <v>6633054</v>
+        <v>6633012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485471</v>
+        <v>122485476</v>
       </c>
       <c r="B9" t="n">
-        <v>92114</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,25 +1569,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558027</v>
+        <v>557809</v>
       </c>
       <c r="R9" t="n">
-        <v>6632721</v>
+        <v>6632935</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,7 +1646,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485472</v>
+        <v>122485470</v>
       </c>
       <c r="B10" t="n">
-        <v>80613</v>
+        <v>92126</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,25 +1685,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557871</v>
+        <v>558025</v>
       </c>
       <c r="R10" t="n">
-        <v>6633116</v>
+        <v>6632894</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,12 +1762,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485460</v>
+        <v>122485471</v>
       </c>
       <c r="B11" t="n">
-        <v>91453</v>
+        <v>92114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,21 +1800,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557653</v>
+        <v>558027</v>
       </c>
       <c r="R11" t="n">
-        <v>6632924</v>
+        <v>6632721</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1873,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485476</v>
+        <v>122485475</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1945,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557809</v>
+        <v>557534</v>
       </c>
       <c r="R12" t="n">
-        <v>6632935</v>
+        <v>6632977</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1999,7 +1989,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2021,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485481</v>
+        <v>122485461</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>90851</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,25 +2023,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557818</v>
+        <v>557922</v>
       </c>
       <c r="R13" t="n">
-        <v>6633012</v>
+        <v>6632643</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,7 +2100,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485470</v>
+        <v>122485472</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>80613</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,25 +2139,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558025</v>
+        <v>557871</v>
       </c>
       <c r="R14" t="n">
-        <v>6632894</v>
+        <v>6633116</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,7 +2216,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485466</v>
+        <v>122485460</v>
       </c>
       <c r="B15" t="n">
-        <v>90833</v>
+        <v>91453</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557665</v>
+        <v>557653</v>
       </c>
       <c r="R15" t="n">
-        <v>6633121</v>
+        <v>6632924</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485475</v>
+        <v>122485467</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>91413</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,25 +2371,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557534</v>
+        <v>557835</v>
       </c>
       <c r="R16" t="n">
-        <v>6632977</v>
+        <v>6633054</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Kvist av gammal gran</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485466</v>
+        <v>122485481</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557665</v>
+        <v>557818</v>
       </c>
       <c r="R7" t="n">
-        <v>6633121</v>
+        <v>6633012</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1441,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485481</v>
+        <v>122485472</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>80614</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1453,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557818</v>
+        <v>557871</v>
       </c>
       <c r="R8" t="n">
-        <v>6633012</v>
+        <v>6633116</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,7 +1530,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485476</v>
+        <v>122485461</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,21 +1573,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557809</v>
+        <v>557922</v>
       </c>
       <c r="R9" t="n">
-        <v>6632935</v>
+        <v>6632643</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485470</v>
+        <v>122485466</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>90834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,25 +1685,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558025</v>
+        <v>557665</v>
       </c>
       <c r="R10" t="n">
-        <v>6632894</v>
+        <v>6633121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,7 +1762,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1784,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485471</v>
+        <v>122485460</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>91454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,21 +1805,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558027</v>
+        <v>557653</v>
       </c>
       <c r="R11" t="n">
-        <v>6632721</v>
+        <v>6632924</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1873,7 +1878,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Granskog, sumpskogsstråk</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1895,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485475</v>
+        <v>122485471</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>92115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,25 +1917,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557534</v>
+        <v>558027</v>
       </c>
       <c r="R12" t="n">
-        <v>6632977</v>
+        <v>6632721</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1984,12 +1994,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Kvist av gammal gran</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485461</v>
+        <v>122485470</v>
       </c>
       <c r="B13" t="n">
-        <v>90851</v>
+        <v>92127</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557922</v>
+        <v>558025</v>
       </c>
       <c r="R13" t="n">
-        <v>6632643</v>
+        <v>6632894</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2101,11 +2106,6 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Äldre tallskog, lav-ristyp</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485472</v>
+        <v>122485467</v>
       </c>
       <c r="B14" t="n">
-        <v>80613</v>
+        <v>91414</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,25 +2139,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>1179</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557871</v>
+        <v>557835</v>
       </c>
       <c r="R14" t="n">
-        <v>6633116</v>
+        <v>6633054</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485460</v>
+        <v>122485475</v>
       </c>
       <c r="B15" t="n">
-        <v>91453</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557653</v>
+        <v>557534</v>
       </c>
       <c r="R15" t="n">
-        <v>6632924</v>
+        <v>6632977</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485467</v>
+        <v>122485476</v>
       </c>
       <c r="B16" t="n">
-        <v>91413</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,25 +2371,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1179</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557835</v>
+        <v>557809</v>
       </c>
       <c r="R16" t="n">
-        <v>6633054</v>
+        <v>6632935</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485481</v>
+        <v>122485470</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>92130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557818</v>
+        <v>558025</v>
       </c>
       <c r="R7" t="n">
-        <v>6633012</v>
+        <v>6632894</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485472</v>
+        <v>122485471</v>
       </c>
       <c r="B8" t="n">
-        <v>80614</v>
+        <v>92118</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,25 +1453,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557871</v>
+        <v>558027</v>
       </c>
       <c r="R8" t="n">
-        <v>6633116</v>
+        <v>6632721</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1530,12 +1530,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485461</v>
+        <v>122485460</v>
       </c>
       <c r="B9" t="n">
-        <v>90852</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,25 +1564,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557922</v>
+        <v>557653</v>
       </c>
       <c r="R9" t="n">
-        <v>6632643</v>
+        <v>6632924</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,12 +1641,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1676,7 +1671,7 @@
         <v>122485466</v>
       </c>
       <c r="B10" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1789,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485460</v>
+        <v>122485475</v>
       </c>
       <c r="B11" t="n">
-        <v>91454</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1796,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557653</v>
+        <v>557534</v>
       </c>
       <c r="R11" t="n">
-        <v>6632924</v>
+        <v>6632977</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1873,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485471</v>
+        <v>122485467</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>91417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,25 +1912,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1179</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1945,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558027</v>
+        <v>557835</v>
       </c>
       <c r="R12" t="n">
-        <v>6632721</v>
+        <v>6633054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,7 +1989,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485470</v>
+        <v>122485472</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>80617</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558025</v>
+        <v>557871</v>
       </c>
       <c r="R13" t="n">
-        <v>6632894</v>
+        <v>6633116</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,7 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2127,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485467</v>
+        <v>122485461</v>
       </c>
       <c r="B14" t="n">
-        <v>91414</v>
+        <v>90855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,25 +2144,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1179</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2167,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557835</v>
+        <v>557922</v>
       </c>
       <c r="R14" t="n">
-        <v>6633054</v>
+        <v>6632643</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2216,12 +2221,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Liggande murken granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2243,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485475</v>
+        <v>122485481</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557534</v>
+        <v>557818</v>
       </c>
       <c r="R15" t="n">
-        <v>6632977</v>
+        <v>6633012</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2333,11 +2338,6 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2362,7 +2362,7 @@
         <v>122485476</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485470</v>
+        <v>122485476</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558025</v>
+        <v>557809</v>
       </c>
       <c r="R7" t="n">
-        <v>6632894</v>
+        <v>6632935</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,7 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485471</v>
+        <v>122485466</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558027</v>
+        <v>557665</v>
       </c>
       <c r="R8" t="n">
-        <v>6632721</v>
+        <v>6633121</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1530,7 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1552,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485460</v>
+        <v>122485461</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,25 +1574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1592,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557653</v>
+        <v>557922</v>
       </c>
       <c r="R9" t="n">
-        <v>6632924</v>
+        <v>6632643</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1641,12 +1651,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1668,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485466</v>
+        <v>122485471</v>
       </c>
       <c r="B10" t="n">
-        <v>90837</v>
+        <v>92118</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1708,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557665</v>
+        <v>558027</v>
       </c>
       <c r="R10" t="n">
-        <v>6633121</v>
+        <v>6632721</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1757,12 +1767,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1784,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485475</v>
+        <v>122485467</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>91417</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,25 +1801,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557534</v>
+        <v>557835</v>
       </c>
       <c r="R11" t="n">
-        <v>6632977</v>
+        <v>6633054</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1873,12 +1878,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Kvist av gammal gran</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485467</v>
+        <v>122485481</v>
       </c>
       <c r="B12" t="n">
-        <v>91417</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,21 +1921,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557835</v>
+        <v>557818</v>
       </c>
       <c r="R12" t="n">
-        <v>6633054</v>
+        <v>6633012</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,12 +1994,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485472</v>
+        <v>122485460</v>
       </c>
       <c r="B13" t="n">
-        <v>80617</v>
+        <v>91457</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557871</v>
+        <v>557653</v>
       </c>
       <c r="R13" t="n">
-        <v>6633116</v>
+        <v>6632924</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485461</v>
+        <v>122485475</v>
       </c>
       <c r="B14" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557922</v>
+        <v>557534</v>
       </c>
       <c r="R14" t="n">
-        <v>6632643</v>
+        <v>6632977</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485481</v>
+        <v>122485470</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>92130</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557818</v>
+        <v>558025</v>
       </c>
       <c r="R15" t="n">
-        <v>6633012</v>
+        <v>6632894</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485476</v>
+        <v>122485472</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>80617</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557809</v>
+        <v>557871</v>
       </c>
       <c r="R16" t="n">
-        <v>6632935</v>
+        <v>6633116</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1678,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485471</v>
+        <v>122485467</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>91417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1179</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558027</v>
+        <v>557835</v>
       </c>
       <c r="R10" t="n">
-        <v>6632721</v>
+        <v>6633054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,7 +1767,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485467</v>
+        <v>122485471</v>
       </c>
       <c r="B11" t="n">
-        <v>91417</v>
+        <v>92118</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1806,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557835</v>
+        <v>558027</v>
       </c>
       <c r="R11" t="n">
-        <v>6633054</v>
+        <v>6632721</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1883,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485466</v>
+        <v>122485461</v>
       </c>
       <c r="B8" t="n">
-        <v>90837</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557665</v>
+        <v>557922</v>
       </c>
       <c r="R8" t="n">
-        <v>6633121</v>
+        <v>6632643</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485461</v>
+        <v>122485466</v>
       </c>
       <c r="B9" t="n">
-        <v>90855</v>
+        <v>90837</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557922</v>
+        <v>557665</v>
       </c>
       <c r="R9" t="n">
-        <v>6632643</v>
+        <v>6633121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485461</v>
+        <v>122485466</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557922</v>
+        <v>557665</v>
       </c>
       <c r="R8" t="n">
-        <v>6632643</v>
+        <v>6633121</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485466</v>
+        <v>122485461</v>
       </c>
       <c r="B9" t="n">
-        <v>90837</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557665</v>
+        <v>557922</v>
       </c>
       <c r="R9" t="n">
-        <v>6633121</v>
+        <v>6632643</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485467</v>
+        <v>122485471</v>
       </c>
       <c r="B10" t="n">
-        <v>91417</v>
+        <v>92118</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557835</v>
+        <v>558027</v>
       </c>
       <c r="R10" t="n">
-        <v>6633054</v>
+        <v>6632721</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,12 +1767,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1794,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485471</v>
+        <v>122485467</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>91417</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1806,25 +1801,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1834,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558027</v>
+        <v>557835</v>
       </c>
       <c r="R11" t="n">
-        <v>6632721</v>
+        <v>6633054</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1883,7 +1878,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485461</v>
+        <v>122485466</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557922</v>
+        <v>557665</v>
       </c>
       <c r="R8" t="n">
-        <v>6632643</v>
+        <v>6633121</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485466</v>
+        <v>122485461</v>
       </c>
       <c r="B9" t="n">
-        <v>90837</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557665</v>
+        <v>557922</v>
       </c>
       <c r="R9" t="n">
-        <v>6633121</v>
+        <v>6632643</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485471</v>
+        <v>122485467</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>91417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1179</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558027</v>
+        <v>557835</v>
       </c>
       <c r="R10" t="n">
-        <v>6632721</v>
+        <v>6633054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,7 +1767,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485467</v>
+        <v>122485471</v>
       </c>
       <c r="B11" t="n">
-        <v>91417</v>
+        <v>92118</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1806,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557835</v>
+        <v>558027</v>
       </c>
       <c r="R11" t="n">
-        <v>6633054</v>
+        <v>6632721</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1883,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485476</v>
+        <v>122485472</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>80719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557809</v>
+        <v>557871</v>
       </c>
       <c r="R7" t="n">
-        <v>6632935</v>
+        <v>6633116</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485461</v>
+        <v>122485460</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>91560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557922</v>
+        <v>557653</v>
       </c>
       <c r="R8" t="n">
-        <v>6632643</v>
+        <v>6632924</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
         <v>122485466</v>
       </c>
       <c r="B9" t="n">
-        <v>90837</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485467</v>
+        <v>122485471</v>
       </c>
       <c r="B10" t="n">
-        <v>91417</v>
+        <v>92221</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557835</v>
+        <v>558027</v>
       </c>
       <c r="R10" t="n">
-        <v>6633054</v>
+        <v>6632721</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,12 +1767,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1794,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485471</v>
+        <v>122485470</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92233</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,21 +1805,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1834,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558027</v>
+        <v>558025</v>
       </c>
       <c r="R11" t="n">
-        <v>6632721</v>
+        <v>6632894</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1905,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485481</v>
+        <v>122485467</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>91520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,21 +1916,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1179</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1945,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557818</v>
+        <v>557835</v>
       </c>
       <c r="R12" t="n">
-        <v>6633012</v>
+        <v>6633054</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,7 +1989,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485460</v>
+        <v>122485461</v>
       </c>
       <c r="B13" t="n">
-        <v>91457</v>
+        <v>90958</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557653</v>
+        <v>557922</v>
       </c>
       <c r="R13" t="n">
-        <v>6632924</v>
+        <v>6632643</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
         <v>122485475</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485470</v>
+        <v>122485481</v>
       </c>
       <c r="B15" t="n">
-        <v>92130</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558025</v>
+        <v>557818</v>
       </c>
       <c r="R15" t="n">
-        <v>6632894</v>
+        <v>6633012</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485472</v>
+        <v>122485476</v>
       </c>
       <c r="B16" t="n">
-        <v>80617</v>
+        <v>78762</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557871</v>
+        <v>557809</v>
       </c>
       <c r="R16" t="n">
-        <v>6633116</v>
+        <v>6632935</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485472</v>
+        <v>122485476</v>
       </c>
       <c r="B7" t="n">
-        <v>80719</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557871</v>
+        <v>557809</v>
       </c>
       <c r="R7" t="n">
-        <v>6633116</v>
+        <v>6632935</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485460</v>
+        <v>122485475</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557653</v>
+        <v>557534</v>
       </c>
       <c r="R8" t="n">
-        <v>6632924</v>
+        <v>6632977</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485466</v>
+        <v>122485470</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>92237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,25 +1574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557665</v>
+        <v>558025</v>
       </c>
       <c r="R9" t="n">
-        <v>6633121</v>
+        <v>6632894</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,12 +1651,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485471</v>
+        <v>122485466</v>
       </c>
       <c r="B10" t="n">
-        <v>92221</v>
+        <v>90944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1685,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558027</v>
+        <v>557665</v>
       </c>
       <c r="R10" t="n">
-        <v>6632721</v>
+        <v>6633121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,7 +1762,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485470</v>
+        <v>122485467</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>91524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1801,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558025</v>
+        <v>557835</v>
       </c>
       <c r="R11" t="n">
-        <v>6632894</v>
+        <v>6633054</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,7 +1878,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485467</v>
+        <v>122485460</v>
       </c>
       <c r="B12" t="n">
-        <v>91520</v>
+        <v>91564</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,25 +1917,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1179</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557835</v>
+        <v>557653</v>
       </c>
       <c r="R12" t="n">
-        <v>6633054</v>
+        <v>6632924</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,12 +1994,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Liggande murken granstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485461</v>
+        <v>122485472</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>80723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,21 +2037,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557922</v>
+        <v>557871</v>
       </c>
       <c r="R13" t="n">
-        <v>6632643</v>
+        <v>6633116</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2110,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485475</v>
+        <v>122485471</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>92225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,25 +2149,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557534</v>
+        <v>558027</v>
       </c>
       <c r="R14" t="n">
-        <v>6632977</v>
+        <v>6632721</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,12 +2226,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Kvist av gammal gran</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
         <v>122485481</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485476</v>
+        <v>122485461</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557809</v>
+        <v>557922</v>
       </c>
       <c r="R16" t="n">
-        <v>6632935</v>
+        <v>6632643</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485476</v>
+        <v>122485481</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557809</v>
+        <v>557818</v>
       </c>
       <c r="R7" t="n">
-        <v>6632935</v>
+        <v>6633012</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1420,11 +1420,6 @@
       <c r="AI7" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485470</v>
+        <v>122485472</v>
       </c>
       <c r="B9" t="n">
-        <v>92237</v>
+        <v>80723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,25 +1569,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558025</v>
+        <v>557871</v>
       </c>
       <c r="R9" t="n">
-        <v>6632894</v>
+        <v>6633116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,7 +1646,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485466</v>
+        <v>122485476</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557665</v>
+        <v>557809</v>
       </c>
       <c r="R10" t="n">
-        <v>6633121</v>
+        <v>6632935</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485467</v>
+        <v>122485470</v>
       </c>
       <c r="B11" t="n">
-        <v>91524</v>
+        <v>92237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1801,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557835</v>
+        <v>558025</v>
       </c>
       <c r="R11" t="n">
-        <v>6633054</v>
+        <v>6632894</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,12 +1878,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485460</v>
+        <v>122485461</v>
       </c>
       <c r="B12" t="n">
-        <v>91564</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,25 +1912,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1945,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557653</v>
+        <v>557922</v>
       </c>
       <c r="R12" t="n">
-        <v>6632924</v>
+        <v>6632643</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1994,12 +1989,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485472</v>
+        <v>122485460</v>
       </c>
       <c r="B13" t="n">
-        <v>80723</v>
+        <v>91564</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557871</v>
+        <v>557653</v>
       </c>
       <c r="R13" t="n">
-        <v>6633116</v>
+        <v>6632924</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,12 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2137,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485471</v>
+        <v>122485466</v>
       </c>
       <c r="B14" t="n">
-        <v>92225</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,25 +2144,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558027</v>
+        <v>557665</v>
       </c>
       <c r="R14" t="n">
-        <v>6632721</v>
+        <v>6633121</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2226,7 +2221,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485481</v>
+        <v>122485471</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557818</v>
+        <v>558027</v>
       </c>
       <c r="R15" t="n">
-        <v>6633012</v>
+        <v>6632721</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485461</v>
+        <v>122485467</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>91524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,25 +2371,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1179</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557922</v>
+        <v>557835</v>
       </c>
       <c r="R16" t="n">
-        <v>6632643</v>
+        <v>6633054</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485481</v>
+        <v>122485472</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>80723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557818</v>
+        <v>557871</v>
       </c>
       <c r="R7" t="n">
-        <v>6633012</v>
+        <v>6633116</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,7 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1557,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485472</v>
+        <v>122485466</v>
       </c>
       <c r="B9" t="n">
-        <v>80723</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,21 +1578,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557871</v>
+        <v>557665</v>
       </c>
       <c r="R9" t="n">
-        <v>6633116</v>
+        <v>6633121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485476</v>
+        <v>122485471</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>92225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,25 +1690,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557809</v>
+        <v>558027</v>
       </c>
       <c r="R10" t="n">
-        <v>6632935</v>
+        <v>6632721</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,12 +1767,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485466</v>
+        <v>122485476</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557665</v>
+        <v>557809</v>
       </c>
       <c r="R14" t="n">
-        <v>6633121</v>
+        <v>6632935</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485471</v>
+        <v>122485467</v>
       </c>
       <c r="B15" t="n">
-        <v>92225</v>
+        <v>91524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1179</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558027</v>
+        <v>557835</v>
       </c>
       <c r="R15" t="n">
-        <v>6632721</v>
+        <v>6633054</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,7 +2337,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485467</v>
+        <v>122485481</v>
       </c>
       <c r="B16" t="n">
-        <v>91524</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,21 +2380,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557835</v>
+        <v>557818</v>
       </c>
       <c r="R16" t="n">
-        <v>6633054</v>
+        <v>6633012</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2453,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485472</v>
+        <v>122485467</v>
       </c>
       <c r="B7" t="n">
-        <v>80723</v>
+        <v>91524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557871</v>
+        <v>557835</v>
       </c>
       <c r="R7" t="n">
-        <v>6633116</v>
+        <v>6633054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485475</v>
+        <v>122485481</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557534</v>
+        <v>557818</v>
       </c>
       <c r="R8" t="n">
-        <v>6632977</v>
+        <v>6633012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1536,11 +1536,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485466</v>
+        <v>122485476</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,21 +1573,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557665</v>
+        <v>557809</v>
       </c>
       <c r="R9" t="n">
-        <v>6633121</v>
+        <v>6632935</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1651,12 +1646,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485471</v>
+        <v>122485475</v>
       </c>
       <c r="B10" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,25 +1685,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558027</v>
+        <v>557534</v>
       </c>
       <c r="R10" t="n">
-        <v>6632721</v>
+        <v>6632977</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,7 +1762,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485470</v>
+        <v>122485471</v>
       </c>
       <c r="B11" t="n">
-        <v>92237</v>
+        <v>92225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,21 +1805,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558025</v>
+        <v>558027</v>
       </c>
       <c r="R11" t="n">
-        <v>6632894</v>
+        <v>6632721</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485461</v>
+        <v>122485460</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>91564</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,25 +1912,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557922</v>
+        <v>557653</v>
       </c>
       <c r="R12" t="n">
-        <v>6632643</v>
+        <v>6632924</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485460</v>
+        <v>122485461</v>
       </c>
       <c r="B13" t="n">
-        <v>91564</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557653</v>
+        <v>557922</v>
       </c>
       <c r="R13" t="n">
-        <v>6632924</v>
+        <v>6632643</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485476</v>
+        <v>122485472</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>80723</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557809</v>
+        <v>557871</v>
       </c>
       <c r="R14" t="n">
-        <v>6632935</v>
+        <v>6633116</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485467</v>
+        <v>122485466</v>
       </c>
       <c r="B15" t="n">
-        <v>91524</v>
+        <v>90944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557835</v>
+        <v>557665</v>
       </c>
       <c r="R15" t="n">
-        <v>6633054</v>
+        <v>6633121</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Liggande murken granstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485481</v>
+        <v>122485470</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>92237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557818</v>
+        <v>558025</v>
       </c>
       <c r="R16" t="n">
-        <v>6633012</v>
+        <v>6632894</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485481</v>
+        <v>122485476</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557818</v>
+        <v>557809</v>
       </c>
       <c r="R8" t="n">
-        <v>6633012</v>
+        <v>6632935</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1536,6 +1536,11 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485476</v>
+        <v>122485481</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,25 +1574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557809</v>
+        <v>557818</v>
       </c>
       <c r="R9" t="n">
-        <v>6632935</v>
+        <v>6633012</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1647,11 +1652,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485461</v>
+        <v>122485472</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>80723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557922</v>
+        <v>557871</v>
       </c>
       <c r="R13" t="n">
-        <v>6632643</v>
+        <v>6633116</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485472</v>
+        <v>122485466</v>
       </c>
       <c r="B14" t="n">
-        <v>80723</v>
+        <v>90944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557871</v>
+        <v>557665</v>
       </c>
       <c r="R14" t="n">
-        <v>6633116</v>
+        <v>6633121</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485466</v>
+        <v>122485461</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557665</v>
+        <v>557922</v>
       </c>
       <c r="R15" t="n">
-        <v>6633121</v>
+        <v>6632643</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485476</v>
+        <v>122485481</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557809</v>
+        <v>557818</v>
       </c>
       <c r="R8" t="n">
-        <v>6632935</v>
+        <v>6633012</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1536,11 +1536,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485481</v>
+        <v>122485476</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,25 +1569,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557818</v>
+        <v>557809</v>
       </c>
       <c r="R9" t="n">
-        <v>6633012</v>
+        <v>6632935</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1652,6 +1647,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485467</v>
+        <v>122485471</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>92233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557835</v>
+        <v>558027</v>
       </c>
       <c r="R7" t="n">
-        <v>6633054</v>
+        <v>6632721</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1441,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485481</v>
+        <v>122485470</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>92245</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1453,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1481,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557818</v>
+        <v>558025</v>
       </c>
       <c r="R8" t="n">
-        <v>6633012</v>
+        <v>6632894</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,7 +1530,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485476</v>
+        <v>122485472</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>80723</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,21 +1568,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557809</v>
+        <v>557871</v>
       </c>
       <c r="R9" t="n">
-        <v>6632935</v>
+        <v>6633116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,12 +1641,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485475</v>
+        <v>122485461</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,21 +1684,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557534</v>
+        <v>557922</v>
       </c>
       <c r="R10" t="n">
-        <v>6632977</v>
+        <v>6632643</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,12 +1757,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Kvist av gammal gran</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1789,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485471</v>
+        <v>122485466</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,25 +1796,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1829,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558027</v>
+        <v>557665</v>
       </c>
       <c r="R11" t="n">
-        <v>6632721</v>
+        <v>6633121</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1878,7 +1873,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485460</v>
+        <v>122485476</v>
       </c>
       <c r="B12" t="n">
-        <v>91564</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,25 +1912,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557653</v>
+        <v>557809</v>
       </c>
       <c r="R12" t="n">
-        <v>6632924</v>
+        <v>6632935</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485472</v>
+        <v>122485481</v>
       </c>
       <c r="B13" t="n">
-        <v>80723</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557871</v>
+        <v>557818</v>
       </c>
       <c r="R13" t="n">
-        <v>6633116</v>
+        <v>6633012</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,12 +2105,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485466</v>
+        <v>122485460</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>91572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,25 +2139,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2172,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557665</v>
+        <v>557653</v>
       </c>
       <c r="R14" t="n">
-        <v>6633121</v>
+        <v>6632924</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2248,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485461</v>
+        <v>122485475</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2264,21 +2259,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557922</v>
+        <v>557534</v>
       </c>
       <c r="R15" t="n">
-        <v>6632643</v>
+        <v>6632977</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,12 +2332,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2364,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485470</v>
+        <v>122485467</v>
       </c>
       <c r="B16" t="n">
-        <v>92237</v>
+        <v>91532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,25 +2371,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>1179</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558025</v>
+        <v>557835</v>
       </c>
       <c r="R16" t="n">
-        <v>6632894</v>
+        <v>6633054</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2453,7 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485471</v>
+        <v>122485472</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>80723</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558027</v>
+        <v>557871</v>
       </c>
       <c r="R7" t="n">
-        <v>6632721</v>
+        <v>6633116</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,7 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485470</v>
+        <v>122485471</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,21 +1462,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558025</v>
+        <v>558027</v>
       </c>
       <c r="R8" t="n">
-        <v>6632894</v>
+        <v>6632721</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1552,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485472</v>
+        <v>122485470</v>
       </c>
       <c r="B9" t="n">
-        <v>80723</v>
+        <v>92245</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,25 +1569,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557871</v>
+        <v>558025</v>
       </c>
       <c r="R9" t="n">
-        <v>6633116</v>
+        <v>6632894</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1641,12 +1646,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485472</v>
+        <v>122485461</v>
       </c>
       <c r="B7" t="n">
-        <v>80723</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557871</v>
+        <v>557922</v>
       </c>
       <c r="R7" t="n">
-        <v>6633116</v>
+        <v>6632643</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485471</v>
+        <v>122485476</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558027</v>
+        <v>557809</v>
       </c>
       <c r="R8" t="n">
-        <v>6632721</v>
+        <v>6632935</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1535,7 +1535,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1557,10 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122485470</v>
+        <v>122485466</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,25 +1574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1597,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558025</v>
+        <v>557665</v>
       </c>
       <c r="R9" t="n">
-        <v>6632894</v>
+        <v>6633121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1646,7 +1651,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1668,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485461</v>
+        <v>122485475</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,21 +1694,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1708,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557922</v>
+        <v>557534</v>
       </c>
       <c r="R10" t="n">
-        <v>6632643</v>
+        <v>6632977</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1757,12 +1767,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1784,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485466</v>
+        <v>122485467</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>91532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,25 +1806,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557665</v>
+        <v>557835</v>
       </c>
       <c r="R11" t="n">
-        <v>6633121</v>
+        <v>6633054</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1873,12 +1883,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485476</v>
+        <v>122485472</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>80723</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,21 +1926,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557809</v>
+        <v>557871</v>
       </c>
       <c r="R12" t="n">
-        <v>6632935</v>
+        <v>6633116</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1989,12 +1999,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2016,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485481</v>
+        <v>122485471</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,25 +2038,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +2066,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557818</v>
+        <v>558027</v>
       </c>
       <c r="R13" t="n">
-        <v>6633012</v>
+        <v>6632721</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2105,7 +2115,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2127,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485460</v>
+        <v>122485481</v>
       </c>
       <c r="B14" t="n">
-        <v>91572</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,25 +2149,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557653</v>
+        <v>557818</v>
       </c>
       <c r="R14" t="n">
-        <v>6632924</v>
+        <v>6633012</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2216,12 +2226,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2243,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485475</v>
+        <v>122485460</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>91572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,25 +2260,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557534</v>
+        <v>557653</v>
       </c>
       <c r="R15" t="n">
-        <v>6632977</v>
+        <v>6632924</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2332,12 +2337,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Granskog, sumpskogsstråk</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Kvist av gammal gran</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2359,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485467</v>
+        <v>122485470</v>
       </c>
       <c r="B16" t="n">
-        <v>91532</v>
+        <v>92245</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2371,25 +2376,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1179</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557835</v>
+        <v>558025</v>
       </c>
       <c r="R16" t="n">
-        <v>6633054</v>
+        <v>6632894</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,12 +2453,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Liggande murken granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 34028-2024 artfynd.xlsx
+++ b/artfynd/A 34028-2024 artfynd.xlsx
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122485461</v>
+        <v>122485467</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>91532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557922</v>
+        <v>557835</v>
       </c>
       <c r="R7" t="n">
-        <v>6632643</v>
+        <v>6633054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre barrskog, frisk blåbärsmark</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Liggande tallstam</t>
+          <t>Liggande murken granstam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122485476</v>
+        <v>122485475</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557809</v>
+        <v>557534</v>
       </c>
       <c r="R8" t="n">
-        <v>6632935</v>
+        <v>6632977</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Kvist av gammal gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122485475</v>
+        <v>122485461</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557534</v>
+        <v>557922</v>
       </c>
       <c r="R10" t="n">
-        <v>6632977</v>
+        <v>6632643</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Kvist av gammal gran</t>
+          <t>Liggande tallstam</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122485467</v>
+        <v>122485472</v>
       </c>
       <c r="B11" t="n">
-        <v>91532</v>
+        <v>80723</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1806,25 +1806,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1179</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557835</v>
+        <v>557871</v>
       </c>
       <c r="R11" t="n">
-        <v>6633054</v>
+        <v>6633116</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre barrskog, frisk blåbärsmark</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Liggande murken granstam</t>
+          <t>Gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485472</v>
+        <v>122485476</v>
       </c>
       <c r="B12" t="n">
-        <v>80723</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557871</v>
+        <v>557809</v>
       </c>
       <c r="R12" t="n">
-        <v>6633116</v>
+        <v>6632935</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Gammal tallhögstubbe</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485471</v>
+        <v>122485481</v>
       </c>
       <c r="B13" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,25 +2038,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558027</v>
+        <v>557818</v>
       </c>
       <c r="R13" t="n">
-        <v>6632721</v>
+        <v>6633012</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Äldre tallskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122485481</v>
+        <v>122485470</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>92245</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,25 +2149,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557818</v>
+        <v>558025</v>
       </c>
       <c r="R14" t="n">
-        <v>6633012</v>
+        <v>6632894</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre tallskog</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122485460</v>
+        <v>122485471</v>
       </c>
       <c r="B15" t="n">
-        <v>91572</v>
+        <v>92233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557653</v>
+        <v>558027</v>
       </c>
       <c r="R15" t="n">
-        <v>6632924</v>
+        <v>6632721</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2337,12 +2337,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granskog, sumpskogsstråk</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre tallskog, lav-ristyp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2364,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122485470</v>
+        <v>122485460</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>91572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2380,21 +2375,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558025</v>
+        <v>557653</v>
       </c>
       <c r="R16" t="n">
-        <v>6632894</v>
+        <v>6632924</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2453,7 +2448,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre tallskog, lav-ristyp</t>
+          <t>Granskog, sumpskogsstråk</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
